--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,56 +899,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135046626</v>
+        <v>137030809</v>
       </c>
       <c r="B4" t="n">
-        <v>57167</v>
+        <v>93451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 29055, Stormandebo, Sm</t>
+          <t>Ugglekärr, Ugglekärr, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579667</v>
+        <v>579651</v>
       </c>
       <c r="R4" t="n">
-        <v>6398807</v>
+        <v>6398895</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,12 +973,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,77 +993,73 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135046626</t>
+          <t>https://artportalen.se/Sighting/137030809</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118890876</v>
+        <v>135046626</v>
       </c>
       <c r="B5" t="n">
-        <v>58114</v>
+        <v>57167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 27145, Ankarsrum, Sm</t>
+          <t>A 29055, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579629</v>
+        <v>579667</v>
       </c>
       <c r="R5" t="n">
-        <v>6398805</v>
+        <v>6398807</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,12 +1083,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,38 +1114,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118890876</t>
+          <t>https://artportalen.se/Sighting/135046626</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119180192</v>
+        <v>137043443</v>
       </c>
       <c r="B6" t="n">
-        <v>58114</v>
+        <v>57195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1157,23 +1154,27 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 27145, Ankarsrum, Sm</t>
+          <t>A 29055, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579673</v>
+        <v>579729</v>
       </c>
       <c r="R6" t="n">
-        <v>6398880</v>
+        <v>6398899</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1200,12 +1201,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,11 +1226,239 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137043443</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118890876</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>579629</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6398805</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118890876</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119180192</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>579673</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6398880</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119180192</t>
         </is>
@@ -1242,6 +1471,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>137030809</v>
       </c>
       <c r="B4" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Lars Engström, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118890909</v>
+        <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96708</v>
+        <v>96792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 27145, Ankarsrum, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579675</v>
+        <v>579615</v>
       </c>
       <c r="R2" t="n">
-        <v>6398816</v>
+        <v>6398979</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,34 +769,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118890909</t>
+          <t>https://artportalen.se/Sighting/137073542</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135046599</v>
+        <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96854</v>
+        <v>96792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,41 +803,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 29055, Stormandebo, Sm</t>
+          <t>Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579642</v>
+        <v>579602</v>
       </c>
       <c r="R3" t="n">
-        <v>6398813</v>
+        <v>6398969</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,17 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Stor kudde!</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,81 +885,75 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135046599</t>
+          <t>https://artportalen.se/Sighting/137074990</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137030809</v>
+        <v>118890909</v>
       </c>
       <c r="B4" t="n">
-        <v>93453</v>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ugglekärr, Ugglekärr, Sm</t>
+          <t>A 27145, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579651</v>
+        <v>579675</v>
       </c>
       <c r="R4" t="n">
-        <v>6398895</v>
+        <v>6398816</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,12 +977,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,33 +991,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström, Gabriel Johansson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137030809</t>
+          <t>https://artportalen.se/Sighting/118890909</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135046626</v>
+        <v>135046599</v>
       </c>
       <c r="B5" t="n">
-        <v>57167</v>
+        <v>96854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,31 +1026,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1053,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579667</v>
+        <v>579642</v>
       </c>
       <c r="R5" t="n">
-        <v>6398807</v>
+        <v>6398813</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,12 +1092,18 @@
           <t>2026-07-10</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stor kudde!</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1114,16 +1121,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135046626</t>
+          <t>https://artportalen.se/Sighting/135046599</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137043443</v>
+        <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>57195</v>
+        <v>96946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,53 +1138,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 29055, Stormandebo, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579729</v>
+        <v>579621</v>
       </c>
       <c r="R6" t="n">
-        <v>6398899</v>
+        <v>6398920</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,9 +1195,19 @@
           <t>2026-10-03</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,77 +1222,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gabriel Johansson</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137043443</t>
+          <t>https://artportalen.se/Sighting/137073545</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118890876</v>
+        <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>58114</v>
+        <v>96946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 27145, Ankarsrum, Sm</t>
+          <t>Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579629</v>
+        <v>579614</v>
       </c>
       <c r="R7" t="n">
-        <v>6398805</v>
+        <v>6398964</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,12 +1304,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,27 +1334,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118890876</t>
+          <t>https://artportalen.se/Sighting/137074995</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119180192</v>
+        <v>137073550</v>
       </c>
       <c r="B8" t="n">
-        <v>58114</v>
+        <v>93059</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,49 +1362,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4745</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 27145, Ankarsrum, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579673</v>
+        <v>579645</v>
       </c>
       <c r="R8" t="n">
-        <v>6398880</v>
+        <v>6398970</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,12 +1416,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,18 +1446,2403 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137073550</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137074998</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93059</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>579652</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6398970</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074998</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137030809</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93453</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ugglekärr, Ugglekärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>579651</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6398895</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars Engström, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137030809</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137073541</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93453</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>579539</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6398978</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073541</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137073546</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93453</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>579622</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6398970</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073546</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137073557</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93453</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>579724</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6398910</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073557</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137073558</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93453</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>579741</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6398918</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073558</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137073559</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93453</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>579765</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6398894</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073559</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137073560</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93453</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>579617</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6398875</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073560</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137074997</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93453</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>579628</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6398971</v>
+      </c>
+      <c r="S17" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074997</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137075000</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93453</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>579760</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6398896</v>
+      </c>
+      <c r="S18" t="n">
+        <v>8</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137075000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137075001</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93453</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>579616</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6398876</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137075001</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137073544</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80101</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>579620</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6398975</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073544</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137073555</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80101</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>579654</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6398900</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073555</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137074993</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80101</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>579597</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6398971</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074993</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135046626</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 29055, Stormandebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>579667</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6398807</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135046626</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137043443</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A 29055, Stormandebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>579729</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6398899</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137043443</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137073556</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>579714</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6398899</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Tupp</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073556</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118890876</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>579629</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6398805</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118890876</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>119180192</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>A 27145, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>579673</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6398880</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-08-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-08-17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/119180192</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137073543</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>579609</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6398948</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073543</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137074992</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>579597</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6398971</v>
+      </c>
+      <c r="S29" t="n">
+        <v>7</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074992</t>
         </is>
       </c>
     </row>
@@ -1473,6 +3855,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137073550</v>
       </c>
       <c r="B8" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137074998</v>
       </c>
       <c r="B9" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137030809</v>
       </c>
       <c r="B10" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>137073541</v>
       </c>
       <c r="B11" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>137073546</v>
       </c>
       <c r="B12" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>137073557</v>
       </c>
       <c r="B13" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137073558</v>
       </c>
       <c r="B14" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137073559</v>
       </c>
       <c r="B15" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137073560</v>
       </c>
       <c r="B16" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137074997</v>
       </c>
       <c r="B17" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>137075000</v>
       </c>
       <c r="B18" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137075001</v>
       </c>
       <c r="B19" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137073544</v>
       </c>
       <c r="B20" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137073555</v>
       </c>
       <c r="B21" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>137074993</v>
       </c>
       <c r="B22" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579597</v>
+        <v>579598</v>
       </c>
       <c r="R22" t="n">
         <v>6398971</v>
@@ -3618,7 +3618,7 @@
         <v>137073543</v>
       </c>
       <c r="B28" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>137074992</v>
       </c>
       <c r="B29" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579597</v>
+        <v>579598</v>
       </c>
       <c r="R29" t="n">
         <v>6398971</v>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137073550</v>
       </c>
       <c r="B8" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137074998</v>
       </c>
       <c r="B9" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137030809</v>
       </c>
       <c r="B10" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>137073541</v>
       </c>
       <c r="B11" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>137073546</v>
       </c>
       <c r="B12" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>137073557</v>
       </c>
       <c r="B13" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137073558</v>
       </c>
       <c r="B14" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137073559</v>
       </c>
       <c r="B15" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137073560</v>
       </c>
       <c r="B16" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137074997</v>
       </c>
       <c r="B17" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>137075000</v>
       </c>
       <c r="B18" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137075001</v>
       </c>
       <c r="B19" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>137073543</v>
       </c>
       <c r="B28" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>137074992</v>
       </c>
       <c r="B29" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137073550</v>
       </c>
       <c r="B8" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137074998</v>
       </c>
       <c r="B9" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137030809</v>
       </c>
       <c r="B10" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>137073541</v>
       </c>
       <c r="B11" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>137073546</v>
       </c>
       <c r="B12" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>137073557</v>
       </c>
       <c r="B13" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137073558</v>
       </c>
       <c r="B14" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137073559</v>
       </c>
       <c r="B15" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137073560</v>
       </c>
       <c r="B16" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137074997</v>
       </c>
       <c r="B17" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>137075000</v>
       </c>
       <c r="B18" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137075001</v>
       </c>
       <c r="B19" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137073544</v>
       </c>
       <c r="B20" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137073555</v>
       </c>
       <c r="B21" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>137074993</v>
       </c>
       <c r="B22" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>137073543</v>
       </c>
       <c r="B28" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>137074992</v>
       </c>
       <c r="B29" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579598</v>
+        <v>579597</v>
       </c>
       <c r="R22" t="n">
         <v>6398971</v>
@@ -3618,7 +3618,7 @@
         <v>137073543</v>
       </c>
       <c r="B28" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>137074992</v>
       </c>
       <c r="B29" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579598</v>
+        <v>579597</v>
       </c>
       <c r="R29" t="n">
         <v>6398971</v>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137073550</v>
       </c>
       <c r="B8" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137074998</v>
       </c>
       <c r="B9" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137030809</v>
       </c>
       <c r="B10" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>137073541</v>
       </c>
       <c r="B11" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>137073546</v>
       </c>
       <c r="B12" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>137073557</v>
       </c>
       <c r="B13" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137073558</v>
       </c>
       <c r="B14" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137073559</v>
       </c>
       <c r="B15" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137073560</v>
       </c>
       <c r="B16" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137074997</v>
       </c>
       <c r="B17" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>137075000</v>
       </c>
       <c r="B18" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137075001</v>
       </c>
       <c r="B19" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137073544</v>
       </c>
       <c r="B20" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137073555</v>
       </c>
       <c r="B21" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>137074993</v>
       </c>
       <c r="B22" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579597</v>
+        <v>579598</v>
       </c>
       <c r="R22" t="n">
         <v>6398971</v>
@@ -3618,7 +3618,7 @@
         <v>137073543</v>
       </c>
       <c r="B28" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>137074992</v>
       </c>
       <c r="B29" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579597</v>
+        <v>579598</v>
       </c>
       <c r="R29" t="n">
         <v>6398971</v>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137073550</v>
       </c>
       <c r="B8" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137074998</v>
       </c>
       <c r="B9" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137030809</v>
       </c>
       <c r="B10" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>137073541</v>
       </c>
       <c r="B11" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>137073546</v>
       </c>
       <c r="B12" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>137073557</v>
       </c>
       <c r="B13" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137073558</v>
       </c>
       <c r="B14" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137073559</v>
       </c>
       <c r="B15" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137073560</v>
       </c>
       <c r="B16" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137074997</v>
       </c>
       <c r="B17" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>137075000</v>
       </c>
       <c r="B18" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137075001</v>
       </c>
       <c r="B19" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137073544</v>
       </c>
       <c r="B20" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137073555</v>
       </c>
       <c r="B21" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>137074993</v>
       </c>
       <c r="B22" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579598</v>
+        <v>579597</v>
       </c>
       <c r="R22" t="n">
         <v>6398971</v>
@@ -3143,7 +3143,7 @@
         <v>137043443</v>
       </c>
       <c r="B24" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>137073556</v>
       </c>
       <c r="B25" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>137073543</v>
       </c>
       <c r="B28" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>137074992</v>
       </c>
       <c r="B29" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579598</v>
+        <v>579597</v>
       </c>
       <c r="R29" t="n">
         <v>6398971</v>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137073550</v>
       </c>
       <c r="B8" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137074998</v>
       </c>
       <c r="B9" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137030809</v>
       </c>
       <c r="B10" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>137073541</v>
       </c>
       <c r="B11" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>137073546</v>
       </c>
       <c r="B12" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>137073557</v>
       </c>
       <c r="B13" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137073558</v>
       </c>
       <c r="B14" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137073559</v>
       </c>
       <c r="B15" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137073560</v>
       </c>
       <c r="B16" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137074997</v>
       </c>
       <c r="B17" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>137075000</v>
       </c>
       <c r="B18" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137075001</v>
       </c>
       <c r="B19" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137073544</v>
       </c>
       <c r="B20" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137073555</v>
       </c>
       <c r="B21" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>137074993</v>
       </c>
       <c r="B22" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579597</v>
+        <v>579598</v>
       </c>
       <c r="R22" t="n">
         <v>6398971</v>
@@ -3143,7 +3143,7 @@
         <v>137043443</v>
       </c>
       <c r="B24" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>137073556</v>
       </c>
       <c r="B25" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>137073543</v>
       </c>
       <c r="B28" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>137074992</v>
       </c>
       <c r="B29" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579597</v>
+        <v>579598</v>
       </c>
       <c r="R29" t="n">
         <v>6398971</v>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -3174,16 +3174,8 @@
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3292,11 +3284,7 @@
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137073550</v>
       </c>
       <c r="B8" t="n">
-        <v>93087</v>
+        <v>93090</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137074998</v>
       </c>
       <c r="B9" t="n">
-        <v>93087</v>
+        <v>93090</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137030809</v>
       </c>
       <c r="B10" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>137073541</v>
       </c>
       <c r="B11" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>137073546</v>
       </c>
       <c r="B12" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>137073557</v>
       </c>
       <c r="B13" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137073558</v>
       </c>
       <c r="B14" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137073559</v>
       </c>
       <c r="B15" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137073560</v>
       </c>
       <c r="B16" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137074997</v>
       </c>
       <c r="B17" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>137075000</v>
       </c>
       <c r="B18" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137075001</v>
       </c>
       <c r="B19" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>137073543</v>
       </c>
       <c r="B28" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>137074992</v>
       </c>
       <c r="B29" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137073550</v>
       </c>
       <c r="B8" t="n">
-        <v>93090</v>
+        <v>93100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137074998</v>
       </c>
       <c r="B9" t="n">
-        <v>93090</v>
+        <v>93100</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137030809</v>
       </c>
       <c r="B10" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>137073541</v>
       </c>
       <c r="B11" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>137073546</v>
       </c>
       <c r="B12" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>137073557</v>
       </c>
       <c r="B13" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137073558</v>
       </c>
       <c r="B14" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137073559</v>
       </c>
       <c r="B15" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137073560</v>
       </c>
       <c r="B16" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137074997</v>
       </c>
       <c r="B17" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>137075000</v>
       </c>
       <c r="B18" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137075001</v>
       </c>
       <c r="B19" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137073544</v>
       </c>
       <c r="B20" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137073555</v>
       </c>
       <c r="B21" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>137074993</v>
       </c>
       <c r="B22" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579598</v>
+        <v>579597</v>
       </c>
       <c r="R22" t="n">
         <v>6398971</v>
@@ -3143,7 +3143,7 @@
         <v>137043443</v>
       </c>
       <c r="B24" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>137073556</v>
       </c>
       <c r="B25" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>137073543</v>
       </c>
       <c r="B28" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>137074992</v>
       </c>
       <c r="B29" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579598</v>
+        <v>579597</v>
       </c>
       <c r="R29" t="n">
         <v>6398971</v>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137073550</v>
       </c>
       <c r="B8" t="n">
-        <v>93100</v>
+        <v>93101</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137074998</v>
       </c>
       <c r="B9" t="n">
-        <v>93100</v>
+        <v>93101</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137030809</v>
       </c>
       <c r="B10" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>137073541</v>
       </c>
       <c r="B11" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>137073546</v>
       </c>
       <c r="B12" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>137073557</v>
       </c>
       <c r="B13" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137073558</v>
       </c>
       <c r="B14" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137073559</v>
       </c>
       <c r="B15" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137073560</v>
       </c>
       <c r="B16" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137074997</v>
       </c>
       <c r="B17" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>137075000</v>
       </c>
       <c r="B18" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137075001</v>
       </c>
       <c r="B19" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579597</v>
+        <v>579598</v>
       </c>
       <c r="R22" t="n">
         <v>6398971</v>
@@ -3606,7 +3606,7 @@
         <v>137073543</v>
       </c>
       <c r="B28" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>137074992</v>
       </c>
       <c r="B29" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579597</v>
+        <v>579598</v>
       </c>
       <c r="R29" t="n">
         <v>6398971</v>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579598</v>
+        <v>579597</v>
       </c>
       <c r="R22" t="n">
         <v>6398971</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579598</v>
+        <v>579597</v>
       </c>
       <c r="R29" t="n">
         <v>6398971</v>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137073550</v>
       </c>
       <c r="B8" t="n">
-        <v>93101</v>
+        <v>93104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137074998</v>
       </c>
       <c r="B9" t="n">
-        <v>93101</v>
+        <v>93104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137030809</v>
       </c>
       <c r="B10" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>137073541</v>
       </c>
       <c r="B11" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>137073546</v>
       </c>
       <c r="B12" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>137073557</v>
       </c>
       <c r="B13" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137073558</v>
       </c>
       <c r="B14" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137073559</v>
       </c>
       <c r="B15" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137073560</v>
       </c>
       <c r="B16" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137074997</v>
       </c>
       <c r="B17" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>137075000</v>
       </c>
       <c r="B18" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137075001</v>
       </c>
       <c r="B19" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137073544</v>
       </c>
       <c r="B20" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137073555</v>
       </c>
       <c r="B21" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>137074993</v>
       </c>
       <c r="B22" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>137043443</v>
       </c>
       <c r="B24" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>137073556</v>
       </c>
       <c r="B25" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>137073543</v>
       </c>
       <c r="B28" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>137074992</v>
       </c>
       <c r="B29" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137073550</v>
       </c>
       <c r="B8" t="n">
-        <v>93104</v>
+        <v>93106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137074998</v>
       </c>
       <c r="B9" t="n">
-        <v>93104</v>
+        <v>93106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137030809</v>
       </c>
       <c r="B10" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>137073541</v>
       </c>
       <c r="B11" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>137073546</v>
       </c>
       <c r="B12" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>137073557</v>
       </c>
       <c r="B13" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137073558</v>
       </c>
       <c r="B14" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137073559</v>
       </c>
       <c r="B15" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137073560</v>
       </c>
       <c r="B16" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137074997</v>
       </c>
       <c r="B17" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>137075000</v>
       </c>
       <c r="B18" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137075001</v>
       </c>
       <c r="B19" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579597</v>
+        <v>579598</v>
       </c>
       <c r="R22" t="n">
         <v>6398971</v>
@@ -3606,7 +3606,7 @@
         <v>137073543</v>
       </c>
       <c r="B28" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>137074992</v>
       </c>
       <c r="B29" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579597</v>
+        <v>579598</v>
       </c>
       <c r="R29" t="n">
         <v>6398971</v>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137073550</v>
       </c>
       <c r="B8" t="n">
-        <v>93106</v>
+        <v>93112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137074998</v>
       </c>
       <c r="B9" t="n">
-        <v>93106</v>
+        <v>93112</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137030809</v>
       </c>
       <c r="B10" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>137073541</v>
       </c>
       <c r="B11" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>137073546</v>
       </c>
       <c r="B12" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>137073557</v>
       </c>
       <c r="B13" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137073558</v>
       </c>
       <c r="B14" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137073559</v>
       </c>
       <c r="B15" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137073560</v>
       </c>
       <c r="B16" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137074997</v>
       </c>
       <c r="B17" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>137075000</v>
       </c>
       <c r="B18" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137075001</v>
       </c>
       <c r="B19" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137073544</v>
       </c>
       <c r="B20" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137073555</v>
       </c>
       <c r="B21" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>137074993</v>
       </c>
       <c r="B22" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>137073543</v>
       </c>
       <c r="B28" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>137074992</v>
       </c>
       <c r="B29" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137073550</v>
       </c>
       <c r="B8" t="n">
-        <v>93112</v>
+        <v>93124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137074998</v>
       </c>
       <c r="B9" t="n">
-        <v>93112</v>
+        <v>93124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137030809</v>
       </c>
       <c r="B10" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>137073541</v>
       </c>
       <c r="B11" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>137073546</v>
       </c>
       <c r="B12" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>137073557</v>
       </c>
       <c r="B13" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137073558</v>
       </c>
       <c r="B14" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137073559</v>
       </c>
       <c r="B15" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137073560</v>
       </c>
       <c r="B16" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137074997</v>
       </c>
       <c r="B17" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>137075000</v>
       </c>
       <c r="B18" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137075001</v>
       </c>
       <c r="B19" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137073544</v>
       </c>
       <c r="B20" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137073555</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>137074993</v>
       </c>
       <c r="B22" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579597</v>
+        <v>579598</v>
       </c>
       <c r="R22" t="n">
         <v>6398971</v>
@@ -3606,7 +3606,7 @@
         <v>137073543</v>
       </c>
       <c r="B28" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>137074992</v>
       </c>
       <c r="B29" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579597</v>
+        <v>579598</v>
       </c>
       <c r="R29" t="n">
         <v>6398971</v>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137073550</v>
       </c>
       <c r="B8" t="n">
-        <v>93124</v>
+        <v>93125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137074998</v>
       </c>
       <c r="B9" t="n">
-        <v>93124</v>
+        <v>93125</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137030809</v>
       </c>
       <c r="B10" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>137073541</v>
       </c>
       <c r="B11" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>137073546</v>
       </c>
       <c r="B12" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>137073557</v>
       </c>
       <c r="B13" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137073558</v>
       </c>
       <c r="B14" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137073559</v>
       </c>
       <c r="B15" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137073560</v>
       </c>
       <c r="B16" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137074997</v>
       </c>
       <c r="B17" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>137075000</v>
       </c>
       <c r="B18" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137075001</v>
       </c>
       <c r="B19" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137073544</v>
       </c>
       <c r="B20" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137073555</v>
       </c>
       <c r="B21" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>137074993</v>
       </c>
       <c r="B22" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>137073543</v>
       </c>
       <c r="B28" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>137074992</v>
       </c>
       <c r="B29" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137073550</v>
       </c>
       <c r="B8" t="n">
-        <v>93125</v>
+        <v>93128</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137074998</v>
       </c>
       <c r="B9" t="n">
-        <v>93125</v>
+        <v>93128</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137030809</v>
       </c>
       <c r="B10" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>137073541</v>
       </c>
       <c r="B11" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>137073546</v>
       </c>
       <c r="B12" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>137073557</v>
       </c>
       <c r="B13" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137073558</v>
       </c>
       <c r="B14" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137073559</v>
       </c>
       <c r="B15" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137073560</v>
       </c>
       <c r="B16" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137074997</v>
       </c>
       <c r="B17" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>137075000</v>
       </c>
       <c r="B18" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137075001</v>
       </c>
       <c r="B19" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137073544</v>
       </c>
       <c r="B20" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137073555</v>
       </c>
       <c r="B21" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>137074993</v>
       </c>
       <c r="B22" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>137073543</v>
       </c>
       <c r="B28" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>137074992</v>
       </c>
       <c r="B29" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 29055-2026 artfynd.xlsx
+++ b/artfynd/A 29055-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073542</v>
       </c>
       <c r="B2" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074990</v>
       </c>
       <c r="B3" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137073545</v>
       </c>
       <c r="B6" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137074995</v>
       </c>
       <c r="B7" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137073550</v>
       </c>
       <c r="B8" t="n">
-        <v>93128</v>
+        <v>93132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137074998</v>
       </c>
       <c r="B9" t="n">
-        <v>93128</v>
+        <v>93132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>137030809</v>
       </c>
       <c r="B10" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>137073541</v>
       </c>
       <c r="B11" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>137073546</v>
       </c>
       <c r="B12" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>137073557</v>
       </c>
       <c r="B13" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>137073558</v>
       </c>
       <c r="B14" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>137073559</v>
       </c>
       <c r="B15" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137073560</v>
       </c>
       <c r="B16" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137074997</v>
       </c>
       <c r="B17" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>137075000</v>
       </c>
       <c r="B18" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>137075001</v>
       </c>
       <c r="B19" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137073544</v>
       </c>
       <c r="B20" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>137073555</v>
       </c>
       <c r="B21" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>137074993</v>
       </c>
       <c r="B22" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>137043443</v>
       </c>
       <c r="B24" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>137073556</v>
       </c>
       <c r="B25" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>137073543</v>
       </c>
       <c r="B28" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>137074992</v>
       </c>
       <c r="B29" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
